--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$17</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1523,6 +1523,51 @@
       </c>
       <c r="C17" t="n">
         <v>37.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>第3批⑩ 补 common/websocket 短板：JwtUtil（签名篡改/伪造签发者/过期语义区分）、TokenBlacklist（只存摘要、TTL=剩余</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>39.98</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 口径变更：接入 lombok.config 排除 Lombok 生成方法（只统计手写逻辑，见上方说明）；同时修复 PageResult.of 对 null </t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>41.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>第3批⑪ 接口层补测：8 个测试类覆盖全部 16 个控制器（消息/订单/收藏/用户认证/资料/管理端/分类/举报与健康）—— 重点验证身份只能取自上下文、未登录</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>45.21</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2125,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -2155,7 +2200,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -2285,7 +2330,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -2350,7 +2395,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2360,7 +2405,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2385,17 +2430,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>中高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中高</t>
         </is>
       </c>
       <c r="B11" t="n">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$20</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1568,6 +1568,21 @@
       </c>
       <c r="C20" t="n">
         <v>45.21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>第3批⑫ 服务层起步：FileServiceImpl（上传四道校验：扩展名 / Content-Type / ★magic number 内容 / 大小，含路径</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>48.4</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2345,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>458</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$21</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1583,6 +1583,21 @@
       </c>
       <c r="C21" t="n">
         <v>48.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>★ 第3批⑫ 推荐服务 RecommendServiceImpl（全项目最大一块，3280 条指令）：21 条覆盖缓存命中/未命中、降级链（候选为空 / 未登录</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>62.88</v>
       </c>
     </row>
   </sheetData>
@@ -2345,7 +2360,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>489</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$22</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1598,6 +1598,21 @@
       </c>
       <c r="C22" t="n">
         <v>62.88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>★ 第3批⑫ 管理端与分类：AdminServiceImpl 23 条（★审核状态机只允许待审核商品、★交易中/已售出不允许下架、★不能禁用自己与其他管理员、★</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>75.15000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2375,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>510</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$23</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1613,6 +1613,21 @@
       </c>
       <c r="C23" t="n">
         <v>75.15000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>★ 第3批⑫ 收尾：认证（★密码只存密文、★并发注册撞唯一索引转 2001、★禁用账号在密码校验前就被挡住、Token 带角色）/ 资料（★手机号唯一且"没改过</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>85.56</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +2390,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>557</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$24</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1628,6 +1628,21 @@
       </c>
       <c r="C24" t="n">
         <v>85.56</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>第4批-⑯ 缓存命中率监控：CacheService 新增 stats()/resetStats()，CacheServiceImpl 加命中/未命中/异常三计</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>85.69</v>
       </c>
     </row>
   </sheetData>
@@ -2390,7 +2405,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -203,7 +203,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'覆盖率提升曲线'!$C$5:$C$25</f>
+              <f>'覆盖率提升曲线'!$C$5:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -487,12 +487,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'机审统计'!$A$12:$A$13</f>
+              <f>'机审统计'!$A$12:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'机审统计'!$B$12:$B$13</f>
+              <f>'机审统计'!$B$12:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'机审统计'!$A$12:$A$13</f>
+              <f>'机审统计'!$A$12:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'机审统计'!$C$12:$C$13</f>
+              <f>'机审统计'!$C$12:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -535,12 +535,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'机审统计'!$A$12:$A$13</f>
+              <f>'机审统计'!$A$12:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'机审统计'!$D$12:$D$13</f>
+              <f>'机审统计'!$D$12:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1643,6 +1643,21 @@
       </c>
       <c r="C25" t="n">
         <v>85.69</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>第6批-㉑ 双向评价（后端）：新增 EvaluationModuleServiceImpl 等 10 个类 + 25 条单测，覆盖规则（只有买卖双方/只有已完成</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>86.06</v>
       </c>
     </row>
   </sheetData>
@@ -2158,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2200,7 +2215,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -2284,42 +2299,58 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>47</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>命中的规则分布（Top 8）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>规则</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>命中条数</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>R2-联系方式</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>R2-联系方式</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>R1-违禁词</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2405,7 +2436,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>640</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9">

--- a/docs/论文图表包.xlsx
+++ b/docs/论文图表包.xlsx
@@ -618,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'测试用例分布'!$A$5:$A$9</f>
+              <f>'测试用例分布'!$A$5:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'测试用例分布'!$B$5:$B$9</f>
+              <f>'测试用例分布'!$B$5:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -2366,7 +2366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2447,6 +2447,16 @@
       </c>
       <c r="B9" t="n">
         <v>76</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>前端组件测试</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
